--- a/invoices/請求書_お中元発送費用_2026.xlsx
+++ b/invoices/請求書_お中元発送費用_2026.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t xml:space="preserve">請　求　書（社内）</t>
   </si>
@@ -251,13 +251,16 @@
     <t xml:space="preserve">品目</t>
   </si>
   <si>
-    <t xml:space="preserve">単価</t>
+    <t xml:space="preserve">単価（税込）</t>
   </si>
   <si>
     <t xml:space="preserve">数量</t>
   </si>
   <si>
-    <t xml:space="preserve">金額</t>
+    <t xml:space="preserve">金額（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税率</t>
   </si>
   <si>
     <t xml:space="preserve">備考</t>
@@ -314,6 +317,25 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（軽減）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2026/7/7 </t>
     </r>
     <r>
@@ -349,16 +371,64 @@
     <t xml:space="preserve">追加分</t>
   </si>
   <si>
-    <t xml:space="preserve">小計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消費税</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―</t>
-  </si>
-  <si>
-    <t xml:space="preserve">税込価格のため内税</t>
+    <t xml:space="preserve">小計（税込）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内消費税額（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込金額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×8/108</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（円未満切捨て）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">合計（税込）</t>
@@ -502,17 +572,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日に発送完了、及川様より売上計上の承認済み。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・ギフトカード（</t>
+      <t xml:space="preserve">日に発送完了、及川様より売上計上の承認済み。ギフトカード（</t>
     </r>
     <r>
       <rPr>
@@ -531,6 +591,36 @@
       </rPr>
       <t xml:space="preserve">件）は追加手配分。</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・適用税率：軽減税率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（飲食料品の譲渡・送料込み・内税）。特定商品引換型ギフトカードのため商品売買として課税。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・酒類や食品以外の物品を含むセットは税率が異なる場合があるため、該当時は経理・税理士に要確認。</t>
   </si>
   <si>
     <r>
@@ -969,7 +1059,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\¥#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1054,21 +1144,8 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Yu Gothic"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <name val="Yu Gothic"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1082,6 +1159,30 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1153,7 +1254,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1198,11 +1299,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1218,36 +1323,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1506,15 +1611,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1526,20 +1632,21 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1549,10 +1656,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -1560,34 +1667,34 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
@@ -1606,172 +1713,210 @@
       <c r="D15" s="10" t="s">
         <v>15</v>
       </c>
+      <c r="E15" s="11" t="str">
+        <f aca="false">"（うち消費税額 8%：¥"&amp;TEXT(E25,"#,##0")&amp;"）"</f>
+        <v>（うち消費税額 8%：¥4,998）</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>21</v>
       </c>
+      <c r="G17" s="13" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="15" t="n">
+      <c r="B18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="16" t="n">
         <v>6980</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="16" t="n">
         <f aca="false">C18*D18</f>
         <v>41880</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>23</v>
+      <c r="F18" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
+      <c r="A19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="15" t="n">
+      <c r="B19" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="16" t="n">
         <v>12800</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="16" t="n">
         <f aca="false">C19*D19</f>
         <v>25600</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="15" t="n">
+      <c r="D24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="16" t="n">
         <f aca="false">SUM(E18:E21)</f>
         <v>67480</v>
       </c>
-      <c r="F24" s="18"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="17" t="s">
+      <c r="D25" s="13" t="s">
         <v>29</v>
       </c>
+      <c r="E25" s="16" t="n">
+        <f aca="false">ROUNDDOWN(E24*8/108,0)</f>
+        <v>4998</v>
+      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="19" t="n">
+      <c r="D26" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="22" t="n">
         <f aca="false">E24</f>
         <v>67480</v>
       </c>
-      <c r="F26" s="18"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
+      <c r="A28" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
     </row>
     <row r="29" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
+      <c r="A29" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
+      <c r="A30" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
+      <c r="A31" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1802,160 +1947,160 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>36</v>
+      <c r="A2" s="24" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="23" t="s">
+      <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="C4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="D4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>21</v>
+      <c r="E4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="C5" s="25" t="s">
         <v>45</v>
       </c>
+      <c r="D5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="C6" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="E6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="14"/>
+      <c r="F8" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="C9" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="D9" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="C10" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="E10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
